--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-19.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-19.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,37 +543,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CSM Slatina x CSC 1599 Selimbar</t>
+          <t>Sociedad B x Mallorca</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CSM Slatina</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CSC 1599 Selimbar</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -582,20 +582,20 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>21.28</v>
+        <v>4.35</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sociedad B x Mallorca</t>
+          <t>Septemvri x Botev Plovdiv</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -661,20 +661,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.35</v>
+        <v>4.55</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -701,37 +701,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Septemvri x Botev Plovdiv</t>
+          <t>Gateshead x Southend</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -740,20 +740,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="L4" t="n">
-        <v>4.55</v>
+        <v>17.86</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -785,22 +785,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>NORWAY 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gateshead x Southend</t>
+          <t>Kristiansund x Rosenborg</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -819,20 +819,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="L5" t="n">
-        <v>17.86</v>
+        <v>20.41</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -864,32 +864,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>SCOTLAND 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kristiansund x Rosenborg</t>
+          <t>Hamilton x Queen of South</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +898,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="K6" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
-        <v>20.41</v>
+        <v>15.62</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -943,22 +943,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SCOTLAND 3</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hamilton x Queen of South</t>
+          <t>Sariyer G.K. x Boluspor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -977,20 +977,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="L7" t="n">
-        <v>15.62</v>
+        <v>15.15</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1017,37 +1017,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sariyer G.K. x Boluspor</t>
+          <t>CD Nacional Funchal x Famalicao</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,20 +1056,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>15.15</v>
+        <v>4.35</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1096,37 +1096,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal x Famalicao</t>
+          <t>FK Novi Pazar x Zemun</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,20 +1135,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>5.6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="L9" t="n">
-        <v>4.35</v>
+        <v>21.74</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1175,37 +1175,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FK Novi Pazar x Zemun</t>
+          <t>Orgryte x Sirius</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Novi Pazar</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1214,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="L10" t="n">
-        <v>21.74</v>
+        <v>15.62</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1254,37 +1254,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>NORWAY 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orgryte x Sirius</t>
+          <t>Molde x Aalesunds</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="K11" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="L11" t="n">
-        <v>15.62</v>
+        <v>17.86</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -1333,27 +1333,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Molde x Aalesunds</t>
+          <t>Zrinjski x Fk Velez Mostar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Fk Velez Mostar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1372,20 +1372,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="K12" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="L12" t="n">
-        <v>17.86</v>
+        <v>20.83</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1412,37 +1412,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zrinjski x Fk Velez Mostar</t>
+          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fk Velez Mostar</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1451,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5.8</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>20.83</v>
+        <v>6.67</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1501,27 +1501,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
+          <t>Maccabi Haifa x Ironi Tiberias</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1530,20 +1530,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="L14" t="n">
-        <v>6.67</v>
+        <v>15.15</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa x Ironi Tiberias</t>
+          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1609,20 +1609,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="L15" t="n">
-        <v>15.15</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1649,37 +1649,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
+          <t>Ajax x Excelsior</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1688,20 +1688,20 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="L16" t="n">
-        <v>20</v>
+        <v>14.29</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1728,37 +1728,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ajax x Excelsior</t>
+          <t>KFC Komarno x Slovan Bratislava</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>KFC Komarno</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1767,20 +1767,20 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="K17" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="L17" t="n">
-        <v>14.29</v>
+        <v>18.52</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1812,22 +1812,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SLOVAKIA 1</t>
+          <t>URUGUAY 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KFC Komarno x Slovan Bratislava</t>
+          <t>Cerro x Penarol</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KFC Komarno</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="L18" t="n">
-        <v>18.52</v>
+        <v>14.29</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
@@ -1886,37 +1886,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>URUGUAY 1</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cerro x Penarol</t>
+          <t>Le Mans x Lorient</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1925,20 +1925,20 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>14.29</v>
+        <v>6.67</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1970,32 +1970,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FRANCE 1</t>
+          <t>IRELAND 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Le Mans x Lorient</t>
+          <t>Sligo Rovers x St Patricks</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2004,20 +2004,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="L20" t="n">
-        <v>6.67</v>
+        <v>20.41</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IRELAND 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sligo Rovers x St Patricks</t>
+          <t>Millonarios x Boyaca Chico</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2083,20 +2083,20 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="K21" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="L21" t="n">
-        <v>20.41</v>
+        <v>17.86</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2128,22 +2128,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Millonarios x Boyaca Chico</t>
+          <t>Sevilla x Barcelona</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2162,20 +2162,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="K22" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="L22" t="n">
-        <v>17.86</v>
+        <v>15.62</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2202,27 +2202,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sevilla x Barcelona</t>
+          <t>Sporting Lisbon x Arouca</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Sporting Lisbon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2241,20 +2241,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="L23" t="n">
-        <v>15.62</v>
+        <v>12.2</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2281,27 +2281,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sporting Lisbon x Arouca</t>
+          <t>Sporting Cristal x Atletico Grau</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Atletico Grau</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2320,20 +2320,20 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="L24" t="n">
-        <v>12.2</v>
+        <v>20.83</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2360,27 +2360,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sporting Cristal x Atletico Grau</t>
+          <t>Vasco da Gama x Coritiba</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atletico Grau</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2399,20 +2399,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="K25" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="L25" t="n">
-        <v>20.83</v>
+        <v>22.22</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2439,37 +2439,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>USA 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vasco da Gama x Coritiba</t>
+          <t>Kansas City x Philadelphia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2478,20 +2478,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>22.22</v>
+        <v>7.14</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>3x4</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="L27" t="n">
-        <v>7.14</v>
+        <v>20.41</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
@@ -2597,37 +2597,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kansas City x Philadelphia</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
+          <t>Atletico MG x Chapecoense</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2636,37 +2628,43 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="K28" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="L28" t="n">
-        <v>20.41</v>
+        <v>10.53</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3x4</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2676,17 +2674,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Atletico MG x Chapecoense</t>
+          <t>CSM Slatina x CSC 1599 Selimbar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2707,20 +2705,20 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="L29" t="n">
-        <v>10.53</v>
+        <v>9.52</v>
       </c>
       <c r="M29" t="n">
         <v>100</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2734,89 +2732,12 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>10.16</v>
+        <v>9.19</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ROMANIA 2</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CSM Slatina x CSC 1599 Selimbar</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Match Odds (Away)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="L30" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="M30" t="n">
-        <v>100</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2x1</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="inlineStr">
         <is>
           <t>LIQUIDADO</t>
         </is>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-19.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -543,37 +553,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SPAIN 2</t>
+          <t>ROMANIA 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sociedad B x Mallorca</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sociedad B</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
+          <t>CSM Slatina x CSC 1599 Selimbar</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -582,37 +584,45 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="L2" t="n">
-        <v>4.35</v>
+        <v>9.52</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,37 +632,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BULGARIA 1</t>
+          <t>JAPAN 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Septemvri x Botev Plovdiv</t>
+          <t>Shimizu x Jef Utd Chiba</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Septemvri</t>
+          <t>Shimizu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Jef Utd Chiba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -667,14 +677,14 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.55</v>
+        <v>9.09</v>
       </c>
       <c r="M3" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x3</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -689,9 +699,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>8.77</v>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,37 +719,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ENGLAND 5</t>
+          <t>JAPAN 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gateshead x Southend</t>
+          <t>Tosu x Iwaki SC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Tosu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Iwaki SC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -740,20 +758,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>17.86</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -768,9 +786,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>8.4</v>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,37 +806,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>SPAIN 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kristiansund x Rosenborg</t>
+          <t>Sociedad B x Mallorca</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -819,20 +845,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5.9</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20.41</v>
+        <v>4.35</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,6 +876,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,37 +887,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SCOTLAND 3</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hamilton x Queen of South</t>
+          <t>Septemvri x Botev Plovdiv</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Septemvri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Queen of South</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +926,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15.62</v>
+        <v>4.55</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4x1</t>
+          <t>0x3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +957,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -943,32 +973,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TURKEY 2</t>
+          <t>ENGLAND 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sariyer G.K. x Boluspor</t>
+          <t>Gateshead x Southend</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sariyer G.K.</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,20 +1007,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="L7" t="n">
-        <v>15.15</v>
+        <v>17.86</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1008,6 +1038,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1049,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>NORWAY 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal x Famalicao</t>
+          <t>Kristiansund x Rosenborg</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Nacional Funchal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,20 +1088,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>5.9</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="L8" t="n">
-        <v>4.35</v>
+        <v>20.41</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0x4</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1087,6 +1119,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1096,27 +1130,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>SCOTLAND 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FK Novi Pazar x Zemun</t>
+          <t>Hamilton x Queen of South</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Novi Pazar</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Queen of South</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1135,20 +1169,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="K9" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="L9" t="n">
-        <v>21.74</v>
+        <v>15.62</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>4x1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1166,6 +1200,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1211,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SWEDEN 1</t>
+          <t>TURKEY 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Orgryte x Sirius</t>
+          <t>Sariyer G.K. x Boluspor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Sariyer G.K.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1250,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="L10" t="n">
-        <v>15.62</v>
+        <v>15.15</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1281,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1292,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NORWAY 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Molde x Aalesunds</t>
+          <t>CD Nacional Funchal x Famalicao</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>CD Nacional Funchal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aalesunds</t>
+          <t>Famalicao</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1331,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>17.86</v>
+        <v>4.35</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>0x4</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1362,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,27 +1373,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOSNIA 1</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zrinjski x Fk Velez Mostar</t>
+          <t>FK Novi Pazar x Zemun</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fk Velez Mostar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1372,20 +1412,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L12" t="n">
-        <v>20.83</v>
+        <v>21.74</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1403,6 +1443,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,37 +1454,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>SWEDEN 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
+          <t>Orgryte x Sirius</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,13 +1493,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="L13" t="n">
-        <v>6.67</v>
+        <v>15.62</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -1482,6 +1524,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1491,27 +1535,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>NORWAY 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maccabi Haifa x Ironi Tiberias</t>
+          <t>Molde x Aalesunds</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Aalesunds</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1530,20 +1574,20 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="L14" t="n">
-        <v>15.15</v>
+        <v>17.86</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3x2</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1561,6 +1605,8 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1570,37 +1616,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ISRAEL 1</t>
+          <t>BULGARIA 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
+          <t>Arda x Cherno More</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1609,20 +1655,20 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1637,9 +1683,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>9.65</v>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1649,27 +1703,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NETHERLANDS 1</t>
+          <t>BOSNIA 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ajax x Excelsior</t>
+          <t>Zrinjski x Fk Velez Mostar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Fk Velez Mostar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1688,20 +1742,20 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="K16" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="L16" t="n">
-        <v>14.29</v>
+        <v>20.83</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1719,6 +1773,8 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1728,37 +1784,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLOVAKIA 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KFC Komarno x Slovan Bratislava</t>
+          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KFC Komarno</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1767,13 +1823,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>18.52</v>
+        <v>6.67</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
@@ -1798,6 +1854,8 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1807,37 +1865,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>URUGUAY 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cerro x Penarol</t>
+          <t>Maccabi Haifa x Ironi Tiberias</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1846,20 +1904,20 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="K18" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="L18" t="n">
-        <v>14.29</v>
+        <v>15.15</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1877,6 +1935,8 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1886,37 +1946,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FRANCE 1</t>
+          <t>ISRAEL 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Le Mans x Lorient</t>
+          <t>Maccabi Netanya x Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1925,20 +1985,20 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L19" t="n">
-        <v>6.67</v>
+        <v>20</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1956,6 +2016,8 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1965,27 +2027,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IRELAND 1</t>
+          <t>NETHERLANDS 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sligo Rovers x St Patricks</t>
+          <t>Ajax x Excelsior</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2004,20 +2066,20 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="L20" t="n">
-        <v>20.41</v>
+        <v>14.29</v>
       </c>
       <c r="M20" t="n">
         <v>100</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2035,6 +2097,8 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2044,37 +2108,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COLOMBIA 1</t>
+          <t>SLOVAKIA 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Millonarios x Boyaca Chico</t>
+          <t>KFC Komarno x Slovan Bratislava</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>KFC Komarno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2083,20 +2147,20 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K21" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="L21" t="n">
-        <v>17.86</v>
+        <v>18.52</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2114,6 +2178,8 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2123,37 +2189,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SPAIN 1</t>
+          <t>URUGUAY 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sevilla x Barcelona</t>
+          <t>Cerro x Penarol</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2162,20 +2228,20 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="L22" t="n">
-        <v>15.62</v>
+        <v>14.29</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2193,6 +2259,8 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2202,37 +2270,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PORTUGAL 1</t>
+          <t>FRANCE 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sporting Lisbon x Arouca</t>
+          <t>Le Mans x Lorient</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2241,20 +2309,20 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12.2</v>
+        <v>6.67</v>
       </c>
       <c r="M23" t="n">
         <v>100</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2272,6 +2340,8 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2281,27 +2351,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PERU 1</t>
+          <t>IRELAND 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sporting Cristal x Atletico Grau</t>
+          <t>Sligo Rovers x St Patricks</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atletico Grau</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2320,20 +2390,20 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K24" t="n">
         <v>1.36</v>
       </c>
       <c r="L24" t="n">
-        <v>20.83</v>
+        <v>20.41</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3x1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2351,6 +2421,8 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2360,27 +2432,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>COLOMBIA 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vasco da Gama x Coritiba</t>
+          <t>Millonarios x Boyaca Chico</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Millonarios</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2399,20 +2471,20 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="K25" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="L25" t="n">
-        <v>22.22</v>
+        <v>17.86</v>
       </c>
       <c r="M25" t="n">
         <v>100</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2430,6 +2502,8 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2439,37 +2513,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kansas City x Philadelphia</t>
+          <t>Sevilla x Barcelona</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Philadelphia</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2478,20 +2552,20 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L26" t="n">
-        <v>7.14</v>
+        <v>15.62</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>3x4</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2509,6 +2583,8 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2518,37 +2594,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA 1</t>
+          <t>BRAZIL 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kansas City x Philadelphia</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
+          <t>Atletico MG x Chapecoense</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2557,37 +2625,45 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="L27" t="n">
-        <v>20.41</v>
+        <v>10.53</v>
       </c>
       <c r="M27" t="n">
         <v>100</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3x4</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2597,29 +2673,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atletico MG x Chapecoense</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+          <t>Sporting Lisbon x Arouca</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Arouca</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2628,43 +2712,39 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="L28" t="n">
-        <v>10.53</v>
+        <v>12.2</v>
       </c>
       <c r="M28" t="n">
         <v>100</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2674,29 +2754,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ROMANIA 2</t>
+          <t>PERU 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CSM Slatina x CSC 1599 Selimbar</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+          <t>Sporting Cristal x Atletico Grau</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sporting Cristal</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Atletico Grau</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2705,43 +2793,282 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="L29" t="n">
-        <v>9.52</v>
+        <v>20.83</v>
       </c>
       <c r="M29" t="n">
         <v>100</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>3x1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>9.19</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Vasco da Gama x Coritiba</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L30" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="M30" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5x0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kansas City x Philadelphia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Correct Score (2x2)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M31" t="n">
+        <v>100</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>3x4</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USA 1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Kansas City x Philadelphia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Match Odds (Home)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>100</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>3x4</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-19.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-19.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,19 +684,19 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -771,19 +771,19 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -1668,19 +1668,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S15" t="n">
